--- a/UTCUTS/A2_Extra_Inputs/A-Xtra_Battery_Replacement.xlsx
+++ b/UTCUTS/A2_Extra_Inputs/A-Xtra_Battery_Replacement.xlsx
@@ -1704,7 +1704,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA6600C3-377D-40F2-9225-666ACEF1FB69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1364BE5C-A988-485A-A080-8AA4A078F19A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
